--- a/recetas/recetas.xlsx
+++ b/recetas/recetas.xlsx
@@ -5,24 +5,41 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichelleEstrada\3D Objects\screenScraping\recetas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MichelleEstrada\3D Objects\tablero_screenScraping\recetas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE166196-21E6-4020-937E-CEFC2D70AB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067921BB-D880-406C-A966-90D46CC3F1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="22140" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="22140" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bebidas" sheetId="2" r:id="rId1"/>
     <sheet name="Platillos" sheetId="3" r:id="rId2"/>
     <sheet name="Sub" sheetId="4" r:id="rId3"/>
+    <sheet name="Extras" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Extras!$A$1:$G$7</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8267" uniqueCount="1456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9254" uniqueCount="1461">
   <si>
     <t>Cafe Americano NC</t>
   </si>
@@ -4390,6 +4407,21 @@
   </si>
   <si>
     <t>Harina para Tempura</t>
+  </si>
+  <si>
+    <t>Chiles toreados</t>
+  </si>
+  <si>
+    <t>Guacamole guarnición</t>
+  </si>
+  <si>
+    <t>Pimientos morrones rojos asados</t>
+  </si>
+  <si>
+    <t>Anguila Japonesa</t>
+  </si>
+  <si>
+    <t>Extras Sushi</t>
   </si>
 </sst>
 </file>
@@ -16911,7 +16943,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G2164"/>
+  <dimension ref="A1:G2409"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
@@ -50308,6 +50340,3072 @@
       </c>
       <c r="F2164" s="8"/>
       <c r="G2164" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2166" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B2166" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2166">
+        <v>455</v>
+      </c>
+      <c r="D2166" t="s">
+        <v>860</v>
+      </c>
+      <c r="E2166" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2166" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2166" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2167">
+        <v>467</v>
+      </c>
+      <c r="D2167" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E2167" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2167" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2167" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2168">
+        <v>536</v>
+      </c>
+      <c r="D2168" t="s">
+        <v>550</v>
+      </c>
+      <c r="E2168" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2168" s="2">
+        <v>21.6</v>
+      </c>
+      <c r="G2168" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2169">
+        <v>556</v>
+      </c>
+      <c r="D2169" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E2169" s="2">
+        <v>5</v>
+      </c>
+      <c r="F2169" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2169" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2170">
+        <v>152</v>
+      </c>
+      <c r="D2170" t="s">
+        <v>552</v>
+      </c>
+      <c r="E2170" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2170" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2170" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2171">
+        <v>174</v>
+      </c>
+      <c r="D2171" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E2171" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2171" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2171" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2173" t="s">
+        <v>445</v>
+      </c>
+      <c r="B2173" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2173">
+        <v>5</v>
+      </c>
+      <c r="D2173" t="s">
+        <v>766</v>
+      </c>
+      <c r="E2173" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2173" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2173" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2174">
+        <v>6</v>
+      </c>
+      <c r="D2174" t="s">
+        <v>854</v>
+      </c>
+      <c r="E2174" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2174" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2174" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2176" t="s">
+        <v>446</v>
+      </c>
+      <c r="B2176" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2176">
+        <v>336</v>
+      </c>
+      <c r="D2176" t="s">
+        <v>781</v>
+      </c>
+      <c r="E2176" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2176" s="2">
+        <v>25</v>
+      </c>
+      <c r="G2176" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2178" t="s">
+        <v>447</v>
+      </c>
+      <c r="B2178" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D2178" t="s">
+        <v>990</v>
+      </c>
+      <c r="E2178" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2178" s="2"/>
+      <c r="G2178" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2180" t="s">
+        <v>448</v>
+      </c>
+      <c r="B2180" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2180">
+        <v>36</v>
+      </c>
+      <c r="D2180" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E2180" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2180" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2180" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2182" t="s">
+        <v>449</v>
+      </c>
+      <c r="B2182" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2182">
+        <v>1713</v>
+      </c>
+      <c r="D2182" t="s">
+        <v>821</v>
+      </c>
+      <c r="E2182" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2182" s="2">
+        <v>25</v>
+      </c>
+      <c r="G2182" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2184" t="s">
+        <v>450</v>
+      </c>
+      <c r="B2184" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2184">
+        <v>2288</v>
+      </c>
+      <c r="D2184" t="s">
+        <v>869</v>
+      </c>
+      <c r="E2184" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2184" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2184" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2186" t="s">
+        <v>437</v>
+      </c>
+      <c r="B2186" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C2186">
+        <v>453</v>
+      </c>
+      <c r="D2186" t="s">
+        <v>806</v>
+      </c>
+      <c r="E2186" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2186" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="G2186" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2188" t="s">
+        <v>451</v>
+      </c>
+      <c r="B2188" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2188">
+        <v>345</v>
+      </c>
+      <c r="D2188" t="s">
+        <v>836</v>
+      </c>
+      <c r="E2188" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2188" s="2">
+        <v>40</v>
+      </c>
+      <c r="G2188" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2190" t="s">
+        <v>452</v>
+      </c>
+      <c r="B2190" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2190">
+        <v>349</v>
+      </c>
+      <c r="D2190" t="s">
+        <v>939</v>
+      </c>
+      <c r="E2190" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2190" s="2">
+        <v>45</v>
+      </c>
+      <c r="G2190" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2192" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B2192" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2192">
+        <v>608</v>
+      </c>
+      <c r="D2192" t="s">
+        <v>782</v>
+      </c>
+      <c r="E2192" s="2">
+        <v>15</v>
+      </c>
+      <c r="F2192" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2192" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2193">
+        <v>628</v>
+      </c>
+      <c r="D2193" t="s">
+        <v>784</v>
+      </c>
+      <c r="E2193" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2193" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2193" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D2194" t="s">
+        <v>492</v>
+      </c>
+      <c r="E2194" s="2">
+        <v>18</v>
+      </c>
+      <c r="F2194" s="2"/>
+      <c r="G2194" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D2195" t="s">
+        <v>957</v>
+      </c>
+      <c r="E2195" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2195" s="2"/>
+      <c r="G2195" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2197" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B2197" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2197">
+        <v>608</v>
+      </c>
+      <c r="D2197" t="s">
+        <v>782</v>
+      </c>
+      <c r="E2197" s="2">
+        <v>15</v>
+      </c>
+      <c r="F2197" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2197" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2198">
+        <v>628</v>
+      </c>
+      <c r="D2198" t="s">
+        <v>784</v>
+      </c>
+      <c r="E2198" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2198" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2198" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D2199" t="s">
+        <v>492</v>
+      </c>
+      <c r="E2199" s="2">
+        <v>18</v>
+      </c>
+      <c r="F2199" s="2"/>
+      <c r="G2199" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D2200" t="s">
+        <v>907</v>
+      </c>
+      <c r="E2200" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2200" s="2"/>
+      <c r="G2200" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2202" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B2202" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C2202">
+        <v>4</v>
+      </c>
+      <c r="D2202" t="s">
+        <v>756</v>
+      </c>
+      <c r="E2202" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2202" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2202" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2203">
+        <v>453</v>
+      </c>
+      <c r="D2203" t="s">
+        <v>806</v>
+      </c>
+      <c r="E2203" s="2">
+        <v>20</v>
+      </c>
+      <c r="F2203" s="2">
+        <v>3</v>
+      </c>
+      <c r="G2203" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2204">
+        <v>473</v>
+      </c>
+      <c r="D2204" t="s">
+        <v>861</v>
+      </c>
+      <c r="E2204" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2204" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2204" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2205">
+        <v>536</v>
+      </c>
+      <c r="D2205" t="s">
+        <v>550</v>
+      </c>
+      <c r="E2205" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2205" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="G2205" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2206">
+        <v>152</v>
+      </c>
+      <c r="D2206" t="s">
+        <v>552</v>
+      </c>
+      <c r="E2206" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2206" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2206" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2208" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2208" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D2208" t="s">
+        <v>865</v>
+      </c>
+      <c r="E2208" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2208" s="2"/>
+      <c r="G2208" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2210" t="s">
+        <v>453</v>
+      </c>
+      <c r="B2210" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2210">
+        <v>4</v>
+      </c>
+      <c r="D2210" t="s">
+        <v>756</v>
+      </c>
+      <c r="E2210" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2210" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2210" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2211">
+        <v>453</v>
+      </c>
+      <c r="D2211" t="s">
+        <v>806</v>
+      </c>
+      <c r="E2211" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2211" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G2211" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2212">
+        <v>473</v>
+      </c>
+      <c r="D2212" t="s">
+        <v>861</v>
+      </c>
+      <c r="E2212" s="2">
+        <v>40</v>
+      </c>
+      <c r="F2212" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2212" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2213">
+        <v>106</v>
+      </c>
+      <c r="D2213" t="s">
+        <v>982</v>
+      </c>
+      <c r="E2213" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2213" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2213" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2214">
+        <v>536</v>
+      </c>
+      <c r="D2214" t="s">
+        <v>550</v>
+      </c>
+      <c r="E2214" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2214" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="G2214" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2215">
+        <v>152</v>
+      </c>
+      <c r="D2215" t="s">
+        <v>552</v>
+      </c>
+      <c r="E2215" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2215" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2215" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2216">
+        <v>159</v>
+      </c>
+      <c r="D2216" t="s">
+        <v>553</v>
+      </c>
+      <c r="E2216" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2216" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2216" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2218" t="s">
+        <v>454</v>
+      </c>
+      <c r="B2218" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2218">
+        <v>4</v>
+      </c>
+      <c r="D2218" t="s">
+        <v>756</v>
+      </c>
+      <c r="E2218" s="2">
+        <v>20</v>
+      </c>
+      <c r="F2218" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2218" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2219">
+        <v>420</v>
+      </c>
+      <c r="D2219" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E2219" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2219" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2219" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2221" t="s">
+        <v>455</v>
+      </c>
+      <c r="B2221" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2221">
+        <v>22</v>
+      </c>
+      <c r="D2221" t="s">
+        <v>696</v>
+      </c>
+      <c r="E2221" s="2">
+        <v>400</v>
+      </c>
+      <c r="F2221" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2221" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2222">
+        <v>499</v>
+      </c>
+      <c r="D2222" t="s">
+        <v>538</v>
+      </c>
+      <c r="E2222" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F2222" s="2">
+        <v>40</v>
+      </c>
+      <c r="G2222" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2223">
+        <v>606</v>
+      </c>
+      <c r="D2223" t="s">
+        <v>835</v>
+      </c>
+      <c r="E2223" s="2">
+        <v>300</v>
+      </c>
+      <c r="F2223" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2223" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2225" t="s">
+        <v>439</v>
+      </c>
+      <c r="B2225" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C2225">
+        <v>608</v>
+      </c>
+      <c r="D2225" t="s">
+        <v>782</v>
+      </c>
+      <c r="E2225" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2225" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2225" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2227" t="s">
+        <v>456</v>
+      </c>
+      <c r="B2227" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D2227" t="s">
+        <v>907</v>
+      </c>
+      <c r="E2227" s="2">
+        <v>120</v>
+      </c>
+      <c r="F2227" s="2"/>
+      <c r="G2227" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D2228" t="s">
+        <v>882</v>
+      </c>
+      <c r="E2228" s="2">
+        <v>120</v>
+      </c>
+      <c r="F2228" s="2"/>
+      <c r="G2228" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2230" t="s">
+        <v>457</v>
+      </c>
+      <c r="B2230" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2230">
+        <v>494</v>
+      </c>
+      <c r="D2230" t="s">
+        <v>793</v>
+      </c>
+      <c r="E2230" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2230" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2230" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2232" t="s">
+        <v>416</v>
+      </c>
+      <c r="B2232" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2232">
+        <v>428</v>
+      </c>
+      <c r="D2232" t="s">
+        <v>767</v>
+      </c>
+      <c r="E2232" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2232" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2232" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2234" t="s">
+        <v>417</v>
+      </c>
+      <c r="B2234" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2234">
+        <v>1713</v>
+      </c>
+      <c r="D2234" t="s">
+        <v>821</v>
+      </c>
+      <c r="E2234" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2234" s="2">
+        <v>20</v>
+      </c>
+      <c r="G2234" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2236" t="s">
+        <v>418</v>
+      </c>
+      <c r="B2236" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2236">
+        <v>415</v>
+      </c>
+      <c r="D2236" t="s">
+        <v>948</v>
+      </c>
+      <c r="E2236" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2236" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2236" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2238" t="s">
+        <v>419</v>
+      </c>
+      <c r="B2238" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2238">
+        <v>336</v>
+      </c>
+      <c r="D2238" t="s">
+        <v>781</v>
+      </c>
+      <c r="E2238" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2238" s="2">
+        <v>20</v>
+      </c>
+      <c r="G2238" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2240" t="s">
+        <v>420</v>
+      </c>
+      <c r="B2240" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2240">
+        <v>345</v>
+      </c>
+      <c r="D2240" t="s">
+        <v>836</v>
+      </c>
+      <c r="E2240" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2240" s="2">
+        <v>40</v>
+      </c>
+      <c r="G2240" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2242" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B2242" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2242">
+        <v>456</v>
+      </c>
+      <c r="D2242" t="s">
+        <v>792</v>
+      </c>
+      <c r="E2242" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2242" s="2">
+        <v>5</v>
+      </c>
+      <c r="G2242" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2244" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2244" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2244">
+        <v>421</v>
+      </c>
+      <c r="D2244" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E2244" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2244" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2244" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2246" t="s">
+        <v>422</v>
+      </c>
+      <c r="B2246" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D2246" t="s">
+        <v>975</v>
+      </c>
+      <c r="E2246" s="2">
+        <v>140</v>
+      </c>
+      <c r="F2246" s="2"/>
+      <c r="G2246" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2248" t="s">
+        <v>423</v>
+      </c>
+      <c r="B2248" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2248">
+        <v>2346</v>
+      </c>
+      <c r="D2248" t="s">
+        <v>611</v>
+      </c>
+      <c r="E2248" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2248" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2248" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2250" t="s">
+        <v>424</v>
+      </c>
+      <c r="B2250" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2250">
+        <v>444</v>
+      </c>
+      <c r="D2250" t="s">
+        <v>833</v>
+      </c>
+      <c r="E2250" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2250" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2250" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2251">
+        <v>498</v>
+      </c>
+      <c r="D2251" t="s">
+        <v>801</v>
+      </c>
+      <c r="E2251" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2251" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2251" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2252">
+        <v>499</v>
+      </c>
+      <c r="D2252" t="s">
+        <v>538</v>
+      </c>
+      <c r="E2252" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2252" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="G2252" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2254" t="s">
+        <v>425</v>
+      </c>
+      <c r="B2254" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2254">
+        <v>4597</v>
+      </c>
+      <c r="D2254" t="s">
+        <v>941</v>
+      </c>
+      <c r="E2254" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2254" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2254" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2256" t="s">
+        <v>426</v>
+      </c>
+      <c r="B2256" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2256">
+        <v>4584</v>
+      </c>
+      <c r="D2256" t="s">
+        <v>951</v>
+      </c>
+      <c r="E2256" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2256" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2256" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2258" t="s">
+        <v>427</v>
+      </c>
+      <c r="B2258" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2258">
+        <v>179</v>
+      </c>
+      <c r="D2258" t="s">
+        <v>906</v>
+      </c>
+      <c r="E2258" s="2">
+        <v>300</v>
+      </c>
+      <c r="F2258" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2258" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2260" t="s">
+        <v>428</v>
+      </c>
+      <c r="B2260" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2260">
+        <v>424</v>
+      </c>
+      <c r="D2260" t="s">
+        <v>946</v>
+      </c>
+      <c r="E2260" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2260" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2260" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2262" t="s">
+        <v>429</v>
+      </c>
+      <c r="B2262" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2262">
+        <v>2165</v>
+      </c>
+      <c r="D2262" t="s">
+        <v>809</v>
+      </c>
+      <c r="E2262" s="2">
+        <v>25</v>
+      </c>
+      <c r="F2262" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2262" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2264" t="s">
+        <v>430</v>
+      </c>
+      <c r="B2264" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2264">
+        <v>2033</v>
+      </c>
+      <c r="D2264" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E2264" s="2">
+        <v>2</v>
+      </c>
+      <c r="F2264" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2264" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2266" t="s">
+        <v>431</v>
+      </c>
+      <c r="B2266" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2266">
+        <v>4533</v>
+      </c>
+      <c r="D2266" t="s">
+        <v>999</v>
+      </c>
+      <c r="E2266" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2266" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2266" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2268" t="s">
+        <v>432</v>
+      </c>
+      <c r="B2268" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2268">
+        <v>90</v>
+      </c>
+      <c r="D2268" t="s">
+        <v>940</v>
+      </c>
+      <c r="E2268" s="2">
+        <v>120</v>
+      </c>
+      <c r="F2268" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2268" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2269">
+        <v>4597</v>
+      </c>
+      <c r="D2269" t="s">
+        <v>941</v>
+      </c>
+      <c r="E2269" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2269" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2269" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2270">
+        <v>2347</v>
+      </c>
+      <c r="D2270" t="s">
+        <v>609</v>
+      </c>
+      <c r="E2270" s="2">
+        <v>175</v>
+      </c>
+      <c r="F2270" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2270" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2272" t="s">
+        <v>433</v>
+      </c>
+      <c r="B2272" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2272">
+        <v>417</v>
+      </c>
+      <c r="D2272" t="s">
+        <v>874</v>
+      </c>
+      <c r="E2272" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2272" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2272" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2274" t="s">
+        <v>434</v>
+      </c>
+      <c r="B2274" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2274">
+        <v>630</v>
+      </c>
+      <c r="D2274" t="s">
+        <v>482</v>
+      </c>
+      <c r="E2274" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2274" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2274" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2276" t="s">
+        <v>435</v>
+      </c>
+      <c r="B2276" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2276">
+        <v>632</v>
+      </c>
+      <c r="D2276" t="s">
+        <v>864</v>
+      </c>
+      <c r="E2276" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2276" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2276" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2278" t="s">
+        <v>458</v>
+      </c>
+      <c r="B2278" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D2278" t="s">
+        <v>785</v>
+      </c>
+      <c r="E2278" s="2">
+        <v>110</v>
+      </c>
+      <c r="F2278" s="2"/>
+      <c r="G2278" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2280" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2280" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D2280" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E2280" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2280" s="2"/>
+      <c r="G2280" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2282" t="s">
+        <v>460</v>
+      </c>
+      <c r="B2282" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D2282" t="s">
+        <v>786</v>
+      </c>
+      <c r="E2282" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2282" s="2"/>
+      <c r="G2282" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2284" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B2284" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D2284" t="s">
+        <v>786</v>
+      </c>
+      <c r="E2284" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2284" s="2"/>
+      <c r="G2284" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2286" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B2286" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2286">
+        <v>615</v>
+      </c>
+      <c r="D2286" t="s">
+        <v>794</v>
+      </c>
+      <c r="E2286" s="2">
+        <v>20</v>
+      </c>
+      <c r="F2286" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2286" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2287">
+        <v>144</v>
+      </c>
+      <c r="D2287" t="s">
+        <v>828</v>
+      </c>
+      <c r="E2287" s="2">
+        <v>120</v>
+      </c>
+      <c r="F2287" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2287" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2288">
+        <v>152</v>
+      </c>
+      <c r="D2288" t="s">
+        <v>552</v>
+      </c>
+      <c r="E2288" s="2">
+        <v>5</v>
+      </c>
+      <c r="F2288" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2288" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2290" t="s">
+        <v>461</v>
+      </c>
+      <c r="B2290" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2290">
+        <v>445</v>
+      </c>
+      <c r="D2290" t="s">
+        <v>895</v>
+      </c>
+      <c r="E2290" s="2">
+        <v>20</v>
+      </c>
+      <c r="F2290" s="2">
+        <v>6</v>
+      </c>
+      <c r="G2290" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2291">
+        <v>450</v>
+      </c>
+      <c r="D2291" t="s">
+        <v>896</v>
+      </c>
+      <c r="E2291" s="2">
+        <v>15</v>
+      </c>
+      <c r="F2291" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="G2291" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2292">
+        <v>453</v>
+      </c>
+      <c r="D2292" t="s">
+        <v>806</v>
+      </c>
+      <c r="E2292" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2292" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G2292" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2293">
+        <v>526</v>
+      </c>
+      <c r="D2293" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E2293" s="2">
+        <v>20</v>
+      </c>
+      <c r="F2293" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2293" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2294">
+        <v>2636</v>
+      </c>
+      <c r="D2294" t="s">
+        <v>808</v>
+      </c>
+      <c r="E2294" s="2">
+        <v>40</v>
+      </c>
+      <c r="F2294" s="2">
+        <v>12</v>
+      </c>
+      <c r="G2294" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2295">
+        <v>605</v>
+      </c>
+      <c r="D2295" t="s">
+        <v>778</v>
+      </c>
+      <c r="E2295" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2295" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="G2295" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2297" t="s">
+        <v>462</v>
+      </c>
+      <c r="B2297" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2297">
+        <v>388</v>
+      </c>
+      <c r="D2297" t="s">
+        <v>702</v>
+      </c>
+      <c r="E2297" s="2">
+        <v>85</v>
+      </c>
+      <c r="F2297" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2297" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2299" t="s">
+        <v>463</v>
+      </c>
+      <c r="B2299" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2299">
+        <v>390</v>
+      </c>
+      <c r="D2299" t="s">
+        <v>703</v>
+      </c>
+      <c r="E2299" s="2">
+        <v>85</v>
+      </c>
+      <c r="F2299" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2299" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2301" t="s">
+        <v>464</v>
+      </c>
+      <c r="B2301" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2301">
+        <v>391</v>
+      </c>
+      <c r="D2301" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E2301" s="2">
+        <v>85</v>
+      </c>
+      <c r="F2301" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2301" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2303" t="s">
+        <v>465</v>
+      </c>
+      <c r="B2303" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2303">
+        <v>393</v>
+      </c>
+      <c r="D2303" t="s">
+        <v>704</v>
+      </c>
+      <c r="E2303" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2303" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2303" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2305" t="s">
+        <v>466</v>
+      </c>
+      <c r="B2305" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2305">
+        <v>417</v>
+      </c>
+      <c r="D2305" t="s">
+        <v>874</v>
+      </c>
+      <c r="E2305" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2305" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2305" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2307" t="s">
+        <v>467</v>
+      </c>
+      <c r="B2307" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2307">
+        <v>528</v>
+      </c>
+      <c r="D2307" t="s">
+        <v>674</v>
+      </c>
+      <c r="E2307" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2307" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2307" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2309" t="s">
+        <v>468</v>
+      </c>
+      <c r="B2309" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2309">
+        <v>428</v>
+      </c>
+      <c r="D2309" t="s">
+        <v>767</v>
+      </c>
+      <c r="E2309" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2309" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G2309" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2311" t="s">
+        <v>469</v>
+      </c>
+      <c r="B2311" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D2311" t="s">
+        <v>909</v>
+      </c>
+      <c r="E2311" s="2">
+        <v>120</v>
+      </c>
+      <c r="F2311" s="2"/>
+      <c r="G2311" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2313" t="s">
+        <v>470</v>
+      </c>
+      <c r="B2313" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2313">
+        <v>4</v>
+      </c>
+      <c r="D2313" t="s">
+        <v>756</v>
+      </c>
+      <c r="E2313" s="2">
+        <v>5</v>
+      </c>
+      <c r="F2313" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2313" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2314">
+        <v>554</v>
+      </c>
+      <c r="D2314" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E2314" s="2">
+        <v>125</v>
+      </c>
+      <c r="F2314" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2314" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2315">
+        <v>152</v>
+      </c>
+      <c r="D2315" t="s">
+        <v>552</v>
+      </c>
+      <c r="E2315" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2315" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2315" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2317" t="s">
+        <v>471</v>
+      </c>
+      <c r="B2317" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2317">
+        <v>132</v>
+      </c>
+      <c r="D2317" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E2317" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2317" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2317" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2319" t="s">
+        <v>472</v>
+      </c>
+      <c r="B2319" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2319">
+        <v>403</v>
+      </c>
+      <c r="D2319" t="s">
+        <v>818</v>
+      </c>
+      <c r="E2319" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2319" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2319" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2321" t="s">
+        <v>473</v>
+      </c>
+      <c r="B2321" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2321">
+        <v>615</v>
+      </c>
+      <c r="D2321" t="s">
+        <v>794</v>
+      </c>
+      <c r="E2321" s="2">
+        <v>20</v>
+      </c>
+      <c r="F2321" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2321" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2322">
+        <v>558</v>
+      </c>
+      <c r="D2322" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E2322" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2322" s="2">
+        <v>25</v>
+      </c>
+      <c r="G2322" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2323">
+        <v>147</v>
+      </c>
+      <c r="D2323" t="s">
+        <v>795</v>
+      </c>
+      <c r="E2323" s="2">
+        <v>15</v>
+      </c>
+      <c r="F2323" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2323" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2324">
+        <v>152</v>
+      </c>
+      <c r="D2324" t="s">
+        <v>552</v>
+      </c>
+      <c r="E2324" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2324" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2324" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2326" t="s">
+        <v>474</v>
+      </c>
+      <c r="B2326" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2326">
+        <v>4477</v>
+      </c>
+      <c r="D2326" t="s">
+        <v>949</v>
+      </c>
+      <c r="E2326" s="2">
+        <v>150</v>
+      </c>
+      <c r="F2326" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2326" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2328" t="s">
+        <v>475</v>
+      </c>
+      <c r="B2328" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2328">
+        <v>402</v>
+      </c>
+      <c r="D2328" t="s">
+        <v>872</v>
+      </c>
+      <c r="E2328" s="2">
+        <v>150</v>
+      </c>
+      <c r="F2328" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2328" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2330" t="s">
+        <v>476</v>
+      </c>
+      <c r="B2330" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2330">
+        <v>453</v>
+      </c>
+      <c r="D2330" t="s">
+        <v>806</v>
+      </c>
+      <c r="E2330" s="2">
+        <v>20</v>
+      </c>
+      <c r="F2330" s="2">
+        <v>3</v>
+      </c>
+      <c r="G2330" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2331">
+        <v>1572</v>
+      </c>
+      <c r="D2331" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E2331" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2331" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2331" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2332">
+        <v>528</v>
+      </c>
+      <c r="D2332" t="s">
+        <v>674</v>
+      </c>
+      <c r="E2332" s="2">
+        <v>20</v>
+      </c>
+      <c r="F2332" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2332" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2333">
+        <v>536</v>
+      </c>
+      <c r="D2333" t="s">
+        <v>550</v>
+      </c>
+      <c r="E2333" s="2">
+        <v>25</v>
+      </c>
+      <c r="F2333" s="2">
+        <v>9</v>
+      </c>
+      <c r="G2333" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2334">
+        <v>152</v>
+      </c>
+      <c r="D2334" t="s">
+        <v>552</v>
+      </c>
+      <c r="E2334" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2334" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2334" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2336" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B2336" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2336">
+        <v>1</v>
+      </c>
+      <c r="D2336" t="s">
+        <v>773</v>
+      </c>
+      <c r="E2336" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2336" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2336" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2337">
+        <v>429</v>
+      </c>
+      <c r="D2337" t="s">
+        <v>774</v>
+      </c>
+      <c r="E2337" s="2">
+        <v>15</v>
+      </c>
+      <c r="F2337" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2337" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2338">
+        <v>567</v>
+      </c>
+      <c r="D2338" t="s">
+        <v>763</v>
+      </c>
+      <c r="E2338" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2338" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2338" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2339">
+        <v>574</v>
+      </c>
+      <c r="D2339" t="s">
+        <v>925</v>
+      </c>
+      <c r="E2339" s="2">
+        <v>350</v>
+      </c>
+      <c r="F2339" s="2">
+        <v>70</v>
+      </c>
+      <c r="G2339" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2341" t="s">
+        <v>477</v>
+      </c>
+      <c r="B2341" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2341">
+        <v>181</v>
+      </c>
+      <c r="D2341" t="s">
+        <v>875</v>
+      </c>
+      <c r="E2341" s="2">
+        <v>90</v>
+      </c>
+      <c r="F2341" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2341" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2343" t="s">
+        <v>478</v>
+      </c>
+      <c r="B2343" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2343">
+        <v>148</v>
+      </c>
+      <c r="D2343" t="s">
+        <v>964</v>
+      </c>
+      <c r="E2343" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2343" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2343" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2344">
+        <v>1372</v>
+      </c>
+      <c r="D2344" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E2344" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2344" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2344" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2346" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2346" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2346">
+        <v>626</v>
+      </c>
+      <c r="D2346" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E2346" s="2">
+        <v>85</v>
+      </c>
+      <c r="F2346" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2346" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2348" t="s">
+        <v>480</v>
+      </c>
+      <c r="B2348" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2348">
+        <v>624</v>
+      </c>
+      <c r="D2348" t="s">
+        <v>922</v>
+      </c>
+      <c r="E2348" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2348" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2348" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2350" t="s">
+        <v>481</v>
+      </c>
+      <c r="B2350" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2350">
+        <v>625</v>
+      </c>
+      <c r="D2350" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E2350" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2350" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2350" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2352" t="s">
+        <v>482</v>
+      </c>
+      <c r="B2352" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2352">
+        <v>630</v>
+      </c>
+      <c r="D2352" t="s">
+        <v>482</v>
+      </c>
+      <c r="E2352" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2352" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2352" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2354" t="s">
+        <v>483</v>
+      </c>
+      <c r="B2354" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2354">
+        <v>631</v>
+      </c>
+      <c r="D2354" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E2354" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2354" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2354" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2356" t="s">
+        <v>484</v>
+      </c>
+      <c r="B2356" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2356">
+        <v>632</v>
+      </c>
+      <c r="D2356" t="s">
+        <v>864</v>
+      </c>
+      <c r="E2356" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2356" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2356" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2358" t="s">
+        <v>440</v>
+      </c>
+      <c r="B2358" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C2358">
+        <v>634</v>
+      </c>
+      <c r="D2358" t="s">
+        <v>829</v>
+      </c>
+      <c r="E2358" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2358" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2358" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2360" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2360" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C2360">
+        <v>632</v>
+      </c>
+      <c r="D2360" t="s">
+        <v>864</v>
+      </c>
+      <c r="E2360" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2360" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2360" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2362" t="s">
+        <v>485</v>
+      </c>
+      <c r="B2362" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2362">
+        <v>588</v>
+      </c>
+      <c r="D2362" t="s">
+        <v>729</v>
+      </c>
+      <c r="E2362" s="2">
+        <v>120</v>
+      </c>
+      <c r="F2362" s="2">
+        <v>36</v>
+      </c>
+      <c r="G2362" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2364" t="s">
+        <v>486</v>
+      </c>
+      <c r="B2364" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2364">
+        <v>1389</v>
+      </c>
+      <c r="D2364" t="s">
+        <v>853</v>
+      </c>
+      <c r="E2364" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2364" s="2">
+        <v>5</v>
+      </c>
+      <c r="G2364" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2366" t="s">
+        <v>487</v>
+      </c>
+      <c r="B2366" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2366">
+        <v>424</v>
+      </c>
+      <c r="D2366" t="s">
+        <v>946</v>
+      </c>
+      <c r="E2366" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2366" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2366" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2368" t="s">
+        <v>442</v>
+      </c>
+      <c r="B2368" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D2368" t="s">
+        <v>882</v>
+      </c>
+      <c r="E2368" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2368" s="2"/>
+      <c r="G2368" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2370" t="s">
+        <v>443</v>
+      </c>
+      <c r="B2370" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D2370" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E2370" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2370" s="2"/>
+      <c r="G2370" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2372" t="s">
+        <v>444</v>
+      </c>
+      <c r="B2372" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D2372" t="s">
+        <v>907</v>
+      </c>
+      <c r="E2372" s="2">
+        <v>60</v>
+      </c>
+      <c r="F2372" s="2"/>
+      <c r="G2372" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2374" t="s">
+        <v>488</v>
+      </c>
+      <c r="B2374" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2374">
+        <v>40</v>
+      </c>
+      <c r="D2374" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E2374" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2374" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2374" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2375">
+        <v>615</v>
+      </c>
+      <c r="D2375" t="s">
+        <v>794</v>
+      </c>
+      <c r="E2375" s="2">
+        <v>40</v>
+      </c>
+      <c r="F2375" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2375" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2376">
+        <v>552</v>
+      </c>
+      <c r="D2376" t="s">
+        <v>917</v>
+      </c>
+      <c r="E2376" s="2">
+        <v>200</v>
+      </c>
+      <c r="F2376" s="2">
+        <v>120</v>
+      </c>
+      <c r="G2376" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2377">
+        <v>173</v>
+      </c>
+      <c r="D2377" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E2377" s="2">
+        <v>10</v>
+      </c>
+      <c r="F2377" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2377" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2379" t="s">
+        <v>489</v>
+      </c>
+      <c r="B2379" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2379">
+        <v>2165</v>
+      </c>
+      <c r="D2379" t="s">
+        <v>809</v>
+      </c>
+      <c r="E2379" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2379" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2379" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2381" t="s">
+        <v>490</v>
+      </c>
+      <c r="B2381" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2381">
+        <v>172</v>
+      </c>
+      <c r="D2381" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E2381" s="2">
+        <v>4</v>
+      </c>
+      <c r="F2381" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2381" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2383" t="s">
+        <v>491</v>
+      </c>
+      <c r="B2383" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2383">
+        <v>637</v>
+      </c>
+      <c r="D2383" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E2383" s="2">
+        <v>4</v>
+      </c>
+      <c r="F2383" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2383" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2385" t="s">
+        <v>492</v>
+      </c>
+      <c r="B2385" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2385">
+        <v>171</v>
+      </c>
+      <c r="D2385" t="s">
+        <v>764</v>
+      </c>
+      <c r="E2385" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2385" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2385" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2387" t="s">
+        <v>436</v>
+      </c>
+      <c r="B2387" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C2387">
+        <v>3803</v>
+      </c>
+      <c r="D2387" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E2387" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2387" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2387" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2388">
+        <v>458</v>
+      </c>
+      <c r="D2388" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E2388" s="2">
+        <v>150</v>
+      </c>
+      <c r="F2388" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2388" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2389">
+        <v>531</v>
+      </c>
+      <c r="D2389" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E2389" s="2">
+        <v>40</v>
+      </c>
+      <c r="F2389" s="2">
+        <v>6</v>
+      </c>
+      <c r="G2389" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2390">
+        <v>493</v>
+      </c>
+      <c r="D2390" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E2390" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2390" s="2">
+        <v>9</v>
+      </c>
+      <c r="G2390" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2391">
+        <v>4537</v>
+      </c>
+      <c r="D2391" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E2391" s="2">
+        <v>80</v>
+      </c>
+      <c r="F2391" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2391" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2393" t="s">
+        <v>493</v>
+      </c>
+      <c r="B2393" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2393">
+        <v>445</v>
+      </c>
+      <c r="D2393" t="s">
+        <v>895</v>
+      </c>
+      <c r="E2393" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2393" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2393" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2394">
+        <v>450</v>
+      </c>
+      <c r="D2394" t="s">
+        <v>896</v>
+      </c>
+      <c r="E2394" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2394" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G2394" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2395">
+        <v>605</v>
+      </c>
+      <c r="D2395" t="s">
+        <v>778</v>
+      </c>
+      <c r="E2395" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2395" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="G2395" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2397" t="s">
+        <v>494</v>
+      </c>
+      <c r="B2397" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2397">
+        <v>643</v>
+      </c>
+      <c r="D2397" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E2397" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2397" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2397" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2399" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B2399" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C2399">
+        <v>3181</v>
+      </c>
+      <c r="D2399" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E2399">
+        <v>30</v>
+      </c>
+      <c r="F2399" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2399" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2401" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B2401" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C2401">
+        <v>2987</v>
+      </c>
+      <c r="D2401" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E2401">
+        <v>45</v>
+      </c>
+      <c r="F2401" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2401" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2402" s="3"/>
+    </row>
+    <row r="2403" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2403" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B2403" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C2403">
+        <v>2990</v>
+      </c>
+      <c r="D2403" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E2403">
+        <v>40</v>
+      </c>
+      <c r="F2403" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2403" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2404" s="3"/>
+    </row>
+    <row r="2405" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2405" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B2405" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C2405">
+        <v>2970</v>
+      </c>
+      <c r="D2405" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E2405">
+        <v>30</v>
+      </c>
+      <c r="F2405" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2405" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2406" s="3"/>
+    </row>
+    <row r="2407" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2407" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B2407" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C2407">
+        <v>662</v>
+      </c>
+      <c r="D2407" t="s">
+        <v>855</v>
+      </c>
+      <c r="E2407">
+        <v>40</v>
+      </c>
+      <c r="F2407" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2407" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2408" s="3"/>
+    </row>
+    <row r="2409" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2409" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B2409" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C2409">
+        <v>2988</v>
+      </c>
+      <c r="D2409" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E2409">
+        <v>40</v>
+      </c>
+      <c r="G2409" s="3" t="s">
         <v>539</v>
       </c>
     </row>
@@ -66260,4 +69358,3085 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB22B9B4-01C9-42F6-87A9-D11D8F8DE682}">
+  <dimension ref="A1:G245"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2">
+        <v>455</v>
+      </c>
+      <c r="D2" t="s">
+        <v>860</v>
+      </c>
+      <c r="E2" s="2">
+        <v>100</v>
+      </c>
+      <c r="F2" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C3">
+        <v>467</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E3" s="2">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C4">
+        <v>536</v>
+      </c>
+      <c r="D4" t="s">
+        <v>550</v>
+      </c>
+      <c r="E4" s="2">
+        <v>60</v>
+      </c>
+      <c r="F4" s="2">
+        <v>21.6</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C5">
+        <v>556</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C6">
+        <v>152</v>
+      </c>
+      <c r="D6" t="s">
+        <v>552</v>
+      </c>
+      <c r="E6" s="2">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <v>174</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E7" s="2">
+        <v>60</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>445</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>766</v>
+      </c>
+      <c r="E9" s="2">
+        <v>50</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C10">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>854</v>
+      </c>
+      <c r="E10" s="2">
+        <v>50</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>446</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C12">
+        <v>336</v>
+      </c>
+      <c r="D12" t="s">
+        <v>781</v>
+      </c>
+      <c r="E12" s="2">
+        <v>100</v>
+      </c>
+      <c r="F12" s="2">
+        <v>25</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>447</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D14" t="s">
+        <v>990</v>
+      </c>
+      <c r="E14" s="2">
+        <v>100</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>448</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C16">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E16" s="2">
+        <v>100</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>449</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C18">
+        <v>1713</v>
+      </c>
+      <c r="D18" t="s">
+        <v>821</v>
+      </c>
+      <c r="E18" s="2">
+        <v>100</v>
+      </c>
+      <c r="F18" s="2">
+        <v>25</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>450</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C20">
+        <v>2288</v>
+      </c>
+      <c r="D20" t="s">
+        <v>869</v>
+      </c>
+      <c r="E20" s="2">
+        <v>100</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>437</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C22">
+        <v>453</v>
+      </c>
+      <c r="D22" t="s">
+        <v>806</v>
+      </c>
+      <c r="E22" s="2">
+        <v>30</v>
+      </c>
+      <c r="F22" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>451</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C24">
+        <v>345</v>
+      </c>
+      <c r="D24" t="s">
+        <v>836</v>
+      </c>
+      <c r="E24" s="2">
+        <v>100</v>
+      </c>
+      <c r="F24" s="2">
+        <v>40</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>452</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C26">
+        <v>349</v>
+      </c>
+      <c r="D26" t="s">
+        <v>939</v>
+      </c>
+      <c r="E26" s="2">
+        <v>100</v>
+      </c>
+      <c r="F26" s="2">
+        <v>45</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C28">
+        <v>608</v>
+      </c>
+      <c r="D28" t="s">
+        <v>782</v>
+      </c>
+      <c r="E28" s="2">
+        <v>15</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C29">
+        <v>628</v>
+      </c>
+      <c r="D29" t="s">
+        <v>784</v>
+      </c>
+      <c r="E29" s="2">
+        <v>10</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>492</v>
+      </c>
+      <c r="E30" s="2">
+        <v>18</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>957</v>
+      </c>
+      <c r="E31" s="2">
+        <v>80</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C33">
+        <v>608</v>
+      </c>
+      <c r="D33" t="s">
+        <v>782</v>
+      </c>
+      <c r="E33" s="2">
+        <v>15</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C34">
+        <v>628</v>
+      </c>
+      <c r="D34" t="s">
+        <v>784</v>
+      </c>
+      <c r="E34" s="2">
+        <v>10</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D35" t="s">
+        <v>492</v>
+      </c>
+      <c r="E35" s="2">
+        <v>18</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D36" t="s">
+        <v>907</v>
+      </c>
+      <c r="E36" s="2">
+        <v>80</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>756</v>
+      </c>
+      <c r="E38" s="2">
+        <v>10</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C39">
+        <v>453</v>
+      </c>
+      <c r="D39" t="s">
+        <v>806</v>
+      </c>
+      <c r="E39" s="2">
+        <v>20</v>
+      </c>
+      <c r="F39" s="2">
+        <v>3</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C40">
+        <v>473</v>
+      </c>
+      <c r="D40" t="s">
+        <v>861</v>
+      </c>
+      <c r="E40" s="2">
+        <v>30</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C41">
+        <v>536</v>
+      </c>
+      <c r="D41" t="s">
+        <v>550</v>
+      </c>
+      <c r="E41" s="2">
+        <v>30</v>
+      </c>
+      <c r="F41" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C42">
+        <v>152</v>
+      </c>
+      <c r="D42" t="s">
+        <v>552</v>
+      </c>
+      <c r="E42" s="2">
+        <v>10</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>438</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D44" t="s">
+        <v>865</v>
+      </c>
+      <c r="E44" s="2">
+        <v>30</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>453</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C46">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
+        <v>756</v>
+      </c>
+      <c r="E46" s="2">
+        <v>10</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C47">
+        <v>453</v>
+      </c>
+      <c r="D47" t="s">
+        <v>806</v>
+      </c>
+      <c r="E47" s="2">
+        <v>10</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C48">
+        <v>473</v>
+      </c>
+      <c r="D48" t="s">
+        <v>861</v>
+      </c>
+      <c r="E48" s="2">
+        <v>40</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C49">
+        <v>106</v>
+      </c>
+      <c r="D49" t="s">
+        <v>982</v>
+      </c>
+      <c r="E49" s="2">
+        <v>10</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C50">
+        <v>536</v>
+      </c>
+      <c r="D50" t="s">
+        <v>550</v>
+      </c>
+      <c r="E50" s="2">
+        <v>30</v>
+      </c>
+      <c r="F50" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C51">
+        <v>152</v>
+      </c>
+      <c r="D51" t="s">
+        <v>552</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C52">
+        <v>159</v>
+      </c>
+      <c r="D52" t="s">
+        <v>553</v>
+      </c>
+      <c r="E52" s="2">
+        <v>10</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>454</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C54">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
+        <v>756</v>
+      </c>
+      <c r="E54" s="2">
+        <v>20</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C55">
+        <v>420</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E55" s="2">
+        <v>80</v>
+      </c>
+      <c r="F55" s="2">
+        <v>0</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>455</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C57">
+        <v>22</v>
+      </c>
+      <c r="D57" t="s">
+        <v>696</v>
+      </c>
+      <c r="E57" s="2">
+        <v>400</v>
+      </c>
+      <c r="F57" s="2">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C58">
+        <v>499</v>
+      </c>
+      <c r="D58" t="s">
+        <v>538</v>
+      </c>
+      <c r="E58" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F58" s="2">
+        <v>40</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C59">
+        <v>606</v>
+      </c>
+      <c r="D59" t="s">
+        <v>835</v>
+      </c>
+      <c r="E59" s="2">
+        <v>300</v>
+      </c>
+      <c r="F59" s="2">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>439</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C61">
+        <v>608</v>
+      </c>
+      <c r="D61" t="s">
+        <v>782</v>
+      </c>
+      <c r="E61" s="2">
+        <v>30</v>
+      </c>
+      <c r="F61" s="2">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>456</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D63" t="s">
+        <v>907</v>
+      </c>
+      <c r="E63" s="2">
+        <v>120</v>
+      </c>
+      <c r="F63" s="2"/>
+      <c r="G63" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D64" t="s">
+        <v>882</v>
+      </c>
+      <c r="E64" s="2">
+        <v>120</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>457</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C66">
+        <v>494</v>
+      </c>
+      <c r="D66" t="s">
+        <v>793</v>
+      </c>
+      <c r="E66" s="2">
+        <v>80</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>416</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C68">
+        <v>428</v>
+      </c>
+      <c r="D68" t="s">
+        <v>767</v>
+      </c>
+      <c r="E68" s="2">
+        <v>60</v>
+      </c>
+      <c r="F68" s="2">
+        <v>15</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>417</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C70">
+        <v>1713</v>
+      </c>
+      <c r="D70" t="s">
+        <v>821</v>
+      </c>
+      <c r="E70" s="2">
+        <v>80</v>
+      </c>
+      <c r="F70" s="2">
+        <v>20</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>418</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C72">
+        <v>415</v>
+      </c>
+      <c r="D72" t="s">
+        <v>948</v>
+      </c>
+      <c r="E72" s="2">
+        <v>100</v>
+      </c>
+      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>419</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C74">
+        <v>336</v>
+      </c>
+      <c r="D74" t="s">
+        <v>781</v>
+      </c>
+      <c r="E74" s="2">
+        <v>80</v>
+      </c>
+      <c r="F74" s="2">
+        <v>20</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>420</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C76">
+        <v>345</v>
+      </c>
+      <c r="D76" t="s">
+        <v>836</v>
+      </c>
+      <c r="E76" s="2">
+        <v>100</v>
+      </c>
+      <c r="F76" s="2">
+        <v>40</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C78">
+        <v>456</v>
+      </c>
+      <c r="D78" t="s">
+        <v>792</v>
+      </c>
+      <c r="E78" s="2">
+        <v>50</v>
+      </c>
+      <c r="F78" s="2">
+        <v>5</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>421</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C80">
+        <v>421</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E80" s="2">
+        <v>60</v>
+      </c>
+      <c r="F80" s="2">
+        <v>0</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>422</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D82" t="s">
+        <v>975</v>
+      </c>
+      <c r="E82" s="2">
+        <v>140</v>
+      </c>
+      <c r="F82" s="2"/>
+      <c r="G82" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>423</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C84">
+        <v>2346</v>
+      </c>
+      <c r="D84" t="s">
+        <v>611</v>
+      </c>
+      <c r="E84" s="2">
+        <v>50</v>
+      </c>
+      <c r="F84" s="2">
+        <v>0</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>424</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C86">
+        <v>444</v>
+      </c>
+      <c r="D86" t="s">
+        <v>833</v>
+      </c>
+      <c r="E86" s="2">
+        <v>30</v>
+      </c>
+      <c r="F86" s="2">
+        <v>0</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C87">
+        <v>498</v>
+      </c>
+      <c r="D87" t="s">
+        <v>801</v>
+      </c>
+      <c r="E87" s="2">
+        <v>30</v>
+      </c>
+      <c r="F87" s="2">
+        <v>0</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C88">
+        <v>499</v>
+      </c>
+      <c r="D88" t="s">
+        <v>538</v>
+      </c>
+      <c r="E88" s="2">
+        <v>80</v>
+      </c>
+      <c r="F88" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>425</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C90">
+        <v>4597</v>
+      </c>
+      <c r="D90" t="s">
+        <v>941</v>
+      </c>
+      <c r="E90" s="2">
+        <v>1</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>426</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C92">
+        <v>4584</v>
+      </c>
+      <c r="D92" t="s">
+        <v>951</v>
+      </c>
+      <c r="E92" s="2">
+        <v>50</v>
+      </c>
+      <c r="F92" s="2">
+        <v>0</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>427</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C94">
+        <v>179</v>
+      </c>
+      <c r="D94" t="s">
+        <v>906</v>
+      </c>
+      <c r="E94" s="2">
+        <v>300</v>
+      </c>
+      <c r="F94" s="2">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>428</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C96">
+        <v>424</v>
+      </c>
+      <c r="D96" t="s">
+        <v>946</v>
+      </c>
+      <c r="E96" s="2">
+        <v>60</v>
+      </c>
+      <c r="F96" s="2">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>429</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C98">
+        <v>2165</v>
+      </c>
+      <c r="D98" t="s">
+        <v>809</v>
+      </c>
+      <c r="E98" s="2">
+        <v>25</v>
+      </c>
+      <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>430</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C100">
+        <v>2033</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E100" s="2">
+        <v>2</v>
+      </c>
+      <c r="F100" s="2">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>431</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C102">
+        <v>4533</v>
+      </c>
+      <c r="D102" t="s">
+        <v>999</v>
+      </c>
+      <c r="E102" s="2">
+        <v>60</v>
+      </c>
+      <c r="F102" s="2">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>432</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C104">
+        <v>90</v>
+      </c>
+      <c r="D104" t="s">
+        <v>940</v>
+      </c>
+      <c r="E104" s="2">
+        <v>120</v>
+      </c>
+      <c r="F104" s="2">
+        <v>0</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C105">
+        <v>4597</v>
+      </c>
+      <c r="D105" t="s">
+        <v>941</v>
+      </c>
+      <c r="E105" s="2">
+        <v>1</v>
+      </c>
+      <c r="F105" s="2">
+        <v>0</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C106">
+        <v>2347</v>
+      </c>
+      <c r="D106" t="s">
+        <v>609</v>
+      </c>
+      <c r="E106" s="2">
+        <v>175</v>
+      </c>
+      <c r="F106" s="2">
+        <v>0</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>433</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C108">
+        <v>417</v>
+      </c>
+      <c r="D108" t="s">
+        <v>874</v>
+      </c>
+      <c r="E108" s="2">
+        <v>50</v>
+      </c>
+      <c r="F108" s="2">
+        <v>0</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>434</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C110">
+        <v>630</v>
+      </c>
+      <c r="D110" t="s">
+        <v>482</v>
+      </c>
+      <c r="E110" s="2">
+        <v>60</v>
+      </c>
+      <c r="F110" s="2">
+        <v>0</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>435</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C112">
+        <v>632</v>
+      </c>
+      <c r="D112" t="s">
+        <v>864</v>
+      </c>
+      <c r="E112" s="2">
+        <v>60</v>
+      </c>
+      <c r="F112" s="2">
+        <v>0</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>458</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D114" t="s">
+        <v>785</v>
+      </c>
+      <c r="E114" s="2">
+        <v>110</v>
+      </c>
+      <c r="F114" s="2"/>
+      <c r="G114" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>459</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E116" s="2">
+        <v>80</v>
+      </c>
+      <c r="F116" s="2"/>
+      <c r="G116" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>460</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D118" t="s">
+        <v>786</v>
+      </c>
+      <c r="E118" s="2">
+        <v>60</v>
+      </c>
+      <c r="F118" s="2"/>
+      <c r="G118" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D120" t="s">
+        <v>786</v>
+      </c>
+      <c r="E120" s="2">
+        <v>60</v>
+      </c>
+      <c r="F120" s="2"/>
+      <c r="G120" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C122">
+        <v>615</v>
+      </c>
+      <c r="D122" t="s">
+        <v>794</v>
+      </c>
+      <c r="E122" s="2">
+        <v>20</v>
+      </c>
+      <c r="F122" s="2">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C123">
+        <v>144</v>
+      </c>
+      <c r="D123" t="s">
+        <v>828</v>
+      </c>
+      <c r="E123" s="2">
+        <v>120</v>
+      </c>
+      <c r="F123" s="2">
+        <v>0</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C124">
+        <v>152</v>
+      </c>
+      <c r="D124" t="s">
+        <v>552</v>
+      </c>
+      <c r="E124" s="2">
+        <v>5</v>
+      </c>
+      <c r="F124" s="2">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>461</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C126">
+        <v>445</v>
+      </c>
+      <c r="D126" t="s">
+        <v>895</v>
+      </c>
+      <c r="E126" s="2">
+        <v>20</v>
+      </c>
+      <c r="F126" s="2">
+        <v>6</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C127">
+        <v>450</v>
+      </c>
+      <c r="D127" t="s">
+        <v>896</v>
+      </c>
+      <c r="E127" s="2">
+        <v>15</v>
+      </c>
+      <c r="F127" s="2">
+        <v>1.65</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C128">
+        <v>453</v>
+      </c>
+      <c r="D128" t="s">
+        <v>806</v>
+      </c>
+      <c r="E128" s="2">
+        <v>10</v>
+      </c>
+      <c r="F128" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C129">
+        <v>526</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E129" s="2">
+        <v>20</v>
+      </c>
+      <c r="F129" s="2">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C130">
+        <v>2636</v>
+      </c>
+      <c r="D130" t="s">
+        <v>808</v>
+      </c>
+      <c r="E130" s="2">
+        <v>40</v>
+      </c>
+      <c r="F130" s="2">
+        <v>12</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C131">
+        <v>605</v>
+      </c>
+      <c r="D131" t="s">
+        <v>778</v>
+      </c>
+      <c r="E131" s="2">
+        <v>30</v>
+      </c>
+      <c r="F131" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>462</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C133">
+        <v>388</v>
+      </c>
+      <c r="D133" t="s">
+        <v>702</v>
+      </c>
+      <c r="E133" s="2">
+        <v>85</v>
+      </c>
+      <c r="F133" s="2">
+        <v>0</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>463</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C135">
+        <v>390</v>
+      </c>
+      <c r="D135" t="s">
+        <v>703</v>
+      </c>
+      <c r="E135" s="2">
+        <v>85</v>
+      </c>
+      <c r="F135" s="2">
+        <v>0</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>464</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C137">
+        <v>391</v>
+      </c>
+      <c r="D137" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E137" s="2">
+        <v>85</v>
+      </c>
+      <c r="F137" s="2">
+        <v>0</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>465</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C139">
+        <v>393</v>
+      </c>
+      <c r="D139" t="s">
+        <v>704</v>
+      </c>
+      <c r="E139" s="2">
+        <v>80</v>
+      </c>
+      <c r="F139" s="2">
+        <v>0</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>466</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C141">
+        <v>417</v>
+      </c>
+      <c r="D141" t="s">
+        <v>874</v>
+      </c>
+      <c r="E141" s="2">
+        <v>60</v>
+      </c>
+      <c r="F141" s="2">
+        <v>0</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>467</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C143">
+        <v>528</v>
+      </c>
+      <c r="D143" t="s">
+        <v>674</v>
+      </c>
+      <c r="E143" s="2">
+        <v>80</v>
+      </c>
+      <c r="F143" s="2">
+        <v>0</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>468</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C145">
+        <v>428</v>
+      </c>
+      <c r="D145" t="s">
+        <v>767</v>
+      </c>
+      <c r="E145" s="2">
+        <v>30</v>
+      </c>
+      <c r="F145" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>469</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D147" t="s">
+        <v>909</v>
+      </c>
+      <c r="E147" s="2">
+        <v>120</v>
+      </c>
+      <c r="F147" s="2"/>
+      <c r="G147" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>470</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C149">
+        <v>4</v>
+      </c>
+      <c r="D149" t="s">
+        <v>756</v>
+      </c>
+      <c r="E149" s="2">
+        <v>5</v>
+      </c>
+      <c r="F149" s="2">
+        <v>0</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C150">
+        <v>554</v>
+      </c>
+      <c r="D150" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E150" s="2">
+        <v>125</v>
+      </c>
+      <c r="F150" s="2">
+        <v>0</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C151">
+        <v>152</v>
+      </c>
+      <c r="D151" t="s">
+        <v>552</v>
+      </c>
+      <c r="E151" s="2">
+        <v>1</v>
+      </c>
+      <c r="F151" s="2">
+        <v>0</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>471</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C153">
+        <v>132</v>
+      </c>
+      <c r="D153" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E153" s="2">
+        <v>100</v>
+      </c>
+      <c r="F153" s="2">
+        <v>0</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>472</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C155">
+        <v>403</v>
+      </c>
+      <c r="D155" t="s">
+        <v>818</v>
+      </c>
+      <c r="E155" s="2">
+        <v>80</v>
+      </c>
+      <c r="F155" s="2">
+        <v>0</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>473</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C157">
+        <v>615</v>
+      </c>
+      <c r="D157" t="s">
+        <v>794</v>
+      </c>
+      <c r="E157" s="2">
+        <v>20</v>
+      </c>
+      <c r="F157" s="2">
+        <v>0</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C158">
+        <v>558</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E158" s="2">
+        <v>100</v>
+      </c>
+      <c r="F158" s="2">
+        <v>25</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C159">
+        <v>147</v>
+      </c>
+      <c r="D159" t="s">
+        <v>795</v>
+      </c>
+      <c r="E159" s="2">
+        <v>15</v>
+      </c>
+      <c r="F159" s="2">
+        <v>0</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C160">
+        <v>152</v>
+      </c>
+      <c r="D160" t="s">
+        <v>552</v>
+      </c>
+      <c r="E160" s="2">
+        <v>50</v>
+      </c>
+      <c r="F160" s="2">
+        <v>0</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>474</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C162">
+        <v>4477</v>
+      </c>
+      <c r="D162" t="s">
+        <v>949</v>
+      </c>
+      <c r="E162" s="2">
+        <v>150</v>
+      </c>
+      <c r="F162" s="2">
+        <v>0</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>475</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C164">
+        <v>402</v>
+      </c>
+      <c r="D164" t="s">
+        <v>872</v>
+      </c>
+      <c r="E164" s="2">
+        <v>150</v>
+      </c>
+      <c r="F164" s="2">
+        <v>0</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>476</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C166">
+        <v>453</v>
+      </c>
+      <c r="D166" t="s">
+        <v>806</v>
+      </c>
+      <c r="E166" s="2">
+        <v>20</v>
+      </c>
+      <c r="F166" s="2">
+        <v>3</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C167">
+        <v>1572</v>
+      </c>
+      <c r="D167" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E167" s="2">
+        <v>10</v>
+      </c>
+      <c r="F167" s="2">
+        <v>0</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C168">
+        <v>528</v>
+      </c>
+      <c r="D168" t="s">
+        <v>674</v>
+      </c>
+      <c r="E168" s="2">
+        <v>20</v>
+      </c>
+      <c r="F168" s="2">
+        <v>0</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C169">
+        <v>536</v>
+      </c>
+      <c r="D169" t="s">
+        <v>550</v>
+      </c>
+      <c r="E169" s="2">
+        <v>25</v>
+      </c>
+      <c r="F169" s="2">
+        <v>9</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C170">
+        <v>152</v>
+      </c>
+      <c r="D170" t="s">
+        <v>552</v>
+      </c>
+      <c r="E170" s="2">
+        <v>1</v>
+      </c>
+      <c r="F170" s="2">
+        <v>0</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172" t="s">
+        <v>773</v>
+      </c>
+      <c r="E172" s="2">
+        <v>30</v>
+      </c>
+      <c r="F172" s="2">
+        <v>0</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C173">
+        <v>429</v>
+      </c>
+      <c r="D173" t="s">
+        <v>774</v>
+      </c>
+      <c r="E173" s="2">
+        <v>15</v>
+      </c>
+      <c r="F173" s="2">
+        <v>0</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C174">
+        <v>567</v>
+      </c>
+      <c r="D174" t="s">
+        <v>763</v>
+      </c>
+      <c r="E174" s="2">
+        <v>10</v>
+      </c>
+      <c r="F174" s="2">
+        <v>0</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C175">
+        <v>574</v>
+      </c>
+      <c r="D175" t="s">
+        <v>925</v>
+      </c>
+      <c r="E175" s="2">
+        <v>350</v>
+      </c>
+      <c r="F175" s="2">
+        <v>70</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>477</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C177">
+        <v>181</v>
+      </c>
+      <c r="D177" t="s">
+        <v>875</v>
+      </c>
+      <c r="E177" s="2">
+        <v>90</v>
+      </c>
+      <c r="F177" s="2">
+        <v>0</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>478</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C179">
+        <v>148</v>
+      </c>
+      <c r="D179" t="s">
+        <v>964</v>
+      </c>
+      <c r="E179" s="2">
+        <v>100</v>
+      </c>
+      <c r="F179" s="2">
+        <v>0</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C180">
+        <v>1372</v>
+      </c>
+      <c r="D180" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E180" s="2">
+        <v>1</v>
+      </c>
+      <c r="F180" s="2">
+        <v>0</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>479</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C182">
+        <v>626</v>
+      </c>
+      <c r="D182" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E182" s="2">
+        <v>85</v>
+      </c>
+      <c r="F182" s="2">
+        <v>0</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>480</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C184">
+        <v>624</v>
+      </c>
+      <c r="D184" t="s">
+        <v>922</v>
+      </c>
+      <c r="E184" s="2">
+        <v>100</v>
+      </c>
+      <c r="F184" s="2">
+        <v>0</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>481</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C186">
+        <v>625</v>
+      </c>
+      <c r="D186" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E186" s="2">
+        <v>80</v>
+      </c>
+      <c r="F186" s="2">
+        <v>0</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>482</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C188">
+        <v>630</v>
+      </c>
+      <c r="D188" t="s">
+        <v>482</v>
+      </c>
+      <c r="E188" s="2">
+        <v>30</v>
+      </c>
+      <c r="F188" s="2">
+        <v>0</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>483</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C190">
+        <v>631</v>
+      </c>
+      <c r="D190" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E190" s="2">
+        <v>50</v>
+      </c>
+      <c r="F190" s="2">
+        <v>0</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>484</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C192">
+        <v>632</v>
+      </c>
+      <c r="D192" t="s">
+        <v>864</v>
+      </c>
+      <c r="E192" s="2">
+        <v>50</v>
+      </c>
+      <c r="F192" s="2">
+        <v>0</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>440</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C194">
+        <v>634</v>
+      </c>
+      <c r="D194" t="s">
+        <v>829</v>
+      </c>
+      <c r="E194" s="2">
+        <v>30</v>
+      </c>
+      <c r="F194" s="2">
+        <v>0</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>441</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C196">
+        <v>632</v>
+      </c>
+      <c r="D196" t="s">
+        <v>864</v>
+      </c>
+      <c r="E196" s="2">
+        <v>60</v>
+      </c>
+      <c r="F196" s="2">
+        <v>0</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>485</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C198">
+        <v>588</v>
+      </c>
+      <c r="D198" t="s">
+        <v>729</v>
+      </c>
+      <c r="E198" s="2">
+        <v>120</v>
+      </c>
+      <c r="F198" s="2">
+        <v>36</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>486</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C200">
+        <v>1389</v>
+      </c>
+      <c r="D200" t="s">
+        <v>853</v>
+      </c>
+      <c r="E200" s="2">
+        <v>100</v>
+      </c>
+      <c r="F200" s="2">
+        <v>5</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>487</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C202">
+        <v>424</v>
+      </c>
+      <c r="D202" t="s">
+        <v>946</v>
+      </c>
+      <c r="E202" s="2">
+        <v>60</v>
+      </c>
+      <c r="F202" s="2">
+        <v>0</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>442</v>
+      </c>
+      <c r="B204" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D204" t="s">
+        <v>882</v>
+      </c>
+      <c r="E204" s="2">
+        <v>60</v>
+      </c>
+      <c r="F204" s="2"/>
+      <c r="G204" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>443</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D206" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E206" s="2">
+        <v>60</v>
+      </c>
+      <c r="F206" s="2"/>
+      <c r="G206" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>444</v>
+      </c>
+      <c r="B208" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D208" t="s">
+        <v>907</v>
+      </c>
+      <c r="E208" s="2">
+        <v>60</v>
+      </c>
+      <c r="F208" s="2"/>
+      <c r="G208" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>488</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C210">
+        <v>40</v>
+      </c>
+      <c r="D210" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E210" s="2">
+        <v>10</v>
+      </c>
+      <c r="F210" s="2">
+        <v>0</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C211">
+        <v>615</v>
+      </c>
+      <c r="D211" t="s">
+        <v>794</v>
+      </c>
+      <c r="E211" s="2">
+        <v>40</v>
+      </c>
+      <c r="F211" s="2">
+        <v>0</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C212">
+        <v>552</v>
+      </c>
+      <c r="D212" t="s">
+        <v>917</v>
+      </c>
+      <c r="E212" s="2">
+        <v>200</v>
+      </c>
+      <c r="F212" s="2">
+        <v>120</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C213">
+        <v>173</v>
+      </c>
+      <c r="D213" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E213" s="2">
+        <v>10</v>
+      </c>
+      <c r="F213" s="2">
+        <v>0</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>489</v>
+      </c>
+      <c r="B215" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C215">
+        <v>2165</v>
+      </c>
+      <c r="D215" t="s">
+        <v>809</v>
+      </c>
+      <c r="E215" s="2">
+        <v>80</v>
+      </c>
+      <c r="F215" s="2">
+        <v>0</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>490</v>
+      </c>
+      <c r="B217" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C217">
+        <v>172</v>
+      </c>
+      <c r="D217" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E217" s="2">
+        <v>4</v>
+      </c>
+      <c r="F217" s="2">
+        <v>0</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>491</v>
+      </c>
+      <c r="B219" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C219">
+        <v>637</v>
+      </c>
+      <c r="D219" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E219" s="2">
+        <v>4</v>
+      </c>
+      <c r="F219" s="2">
+        <v>0</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>492</v>
+      </c>
+      <c r="B221" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C221">
+        <v>171</v>
+      </c>
+      <c r="D221" t="s">
+        <v>764</v>
+      </c>
+      <c r="E221" s="2">
+        <v>50</v>
+      </c>
+      <c r="F221" s="2">
+        <v>0</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>436</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C223">
+        <v>3803</v>
+      </c>
+      <c r="D223" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E223" s="2">
+        <v>50</v>
+      </c>
+      <c r="F223" s="2">
+        <v>0</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C224">
+        <v>458</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E224" s="2">
+        <v>150</v>
+      </c>
+      <c r="F224" s="2">
+        <v>0</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C225">
+        <v>531</v>
+      </c>
+      <c r="D225" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E225" s="2">
+        <v>40</v>
+      </c>
+      <c r="F225" s="2">
+        <v>6</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C226">
+        <v>493</v>
+      </c>
+      <c r="D226" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E226" s="2">
+        <v>30</v>
+      </c>
+      <c r="F226" s="2">
+        <v>9</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C227">
+        <v>4537</v>
+      </c>
+      <c r="D227" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E227" s="2">
+        <v>80</v>
+      </c>
+      <c r="F227" s="2">
+        <v>0</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>493</v>
+      </c>
+      <c r="B229" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C229">
+        <v>445</v>
+      </c>
+      <c r="D229" t="s">
+        <v>895</v>
+      </c>
+      <c r="E229" s="2">
+        <v>50</v>
+      </c>
+      <c r="F229" s="2">
+        <v>15</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C230">
+        <v>450</v>
+      </c>
+      <c r="D230" t="s">
+        <v>896</v>
+      </c>
+      <c r="E230" s="2">
+        <v>50</v>
+      </c>
+      <c r="F230" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C231">
+        <v>605</v>
+      </c>
+      <c r="D231" t="s">
+        <v>778</v>
+      </c>
+      <c r="E231" s="2">
+        <v>50</v>
+      </c>
+      <c r="F231" s="2">
+        <v>32.5</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>494</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C233">
+        <v>643</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E233" s="2">
+        <v>100</v>
+      </c>
+      <c r="F233" s="2">
+        <v>0</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B235" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C235">
+        <v>3181</v>
+      </c>
+      <c r="D235" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E235">
+        <v>30</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C237">
+        <v>2987</v>
+      </c>
+      <c r="D237" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E237">
+        <v>45</v>
+      </c>
+      <c r="G237" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C239">
+        <v>2990</v>
+      </c>
+      <c r="D239" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E239">
+        <v>40</v>
+      </c>
+      <c r="G239" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C241">
+        <v>2970</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E241">
+        <v>30</v>
+      </c>
+      <c r="G241" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C243">
+        <v>662</v>
+      </c>
+      <c r="D243" t="s">
+        <v>855</v>
+      </c>
+      <c r="E243">
+        <v>40</v>
+      </c>
+      <c r="G243" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C245">
+        <v>2988</v>
+      </c>
+      <c r="D245" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E245">
+        <v>40</v>
+      </c>
+      <c r="G245" t="s">
+        <v>539</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G7" xr:uid="{EB22B9B4-01C9-42F6-87A9-D11D8F8DE682}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>